--- a/AAII_Financials/Quarterly/BRK.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRK.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>BRK.A</t>
   </si>
@@ -656,516 +656,528 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>101808000</v>
+      </c>
+      <c r="E8" s="3">
         <v>93675000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>94232000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>94972000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>92515000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>89725000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>94916000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>92995000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>93653000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>89869000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>93376000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>93210000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>92503000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>85393000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>78072000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>76904000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>76201000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>70843000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>71907000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>70583000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>69114000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>64599000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>64381000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>63024000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>56840000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>61265000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>65368000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>64972000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>63598000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>60678000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>63714000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>63450000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>62200000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>58473000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>58800000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>59507000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>57256000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>64370000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>57673000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>58843000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9628000</v>
+      </c>
+      <c r="E9" s="3">
         <v>9096000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9078000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9556000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9036000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8810000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9397000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9415000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9434000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9046000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-26737000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23376000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23362000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18878000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>61786000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>61632000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>58418000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>55806000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>56226000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>55870000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>53250000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>49969000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>50777000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>49279000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>43879000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>47995000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>52436000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>49522000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>49015000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>47445000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>48046000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>50060000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>48686000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>46979000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>52472000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>49418000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>45709000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>54113000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>43559000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>43076000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>33150000</v>
+      </c>
+      <c r="E10" s="3">
         <v>13444000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31055000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39036000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20748000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6279000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24591000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33500000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39115000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>16529000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>47702000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-15961000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>46173000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>45282000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16286000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>15272000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17783000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>15037000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>15681000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>14713000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>15864000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14630000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13604000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>13745000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>12961000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13270000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>12932000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>15450000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>14583000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13233000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>15668000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13390000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13514000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>11494000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6328000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>10089000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>11547000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>10257000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>14114000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>15767000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1330,8 +1343,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1452,8 +1468,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1496,20 +1515,20 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1517,20 +1536,20 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>25000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>10634000</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1547,8 +1566,8 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1574,53 +1593,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3606000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3510000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3549000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3333000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3329000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3265000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3283000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3206000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3198000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3168000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3129000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3210000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3096000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3051000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1696,8 +1718,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,252 +1762,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>68658000</v>
+      </c>
+      <c r="E17" s="3">
         <v>80231000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>63177000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>55936000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>71767000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>83446000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>70325000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>59495000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54538000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>73340000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>45674000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>109171000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46330000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40111000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>71331000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>68112000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>64794000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>62247000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63592000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63397000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>60934000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>56022000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>58725000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>56966000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>61259000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>54339000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>60118000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>56053000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>56011000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>53521000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>57716000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>55325000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>53791000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>52382000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>54654000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>55147000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>51698000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>59738000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>49282000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>48543000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>33150000</v>
+      </c>
+      <c r="E18" s="3">
         <v>13444000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>31055000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39036000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20748000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6279000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24591000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33500000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>39115000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16529000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47702000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15961000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46173000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>45282000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6741000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8792000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11407000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8596000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8315000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7186000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8180000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8577000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5656000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6058000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4419000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6926000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5250000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8919000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7587000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>7157000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5998000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8125000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8409000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6091000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4146000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>4360000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>5558000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>4632000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>8391000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>10300000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2025,297 +2057,304 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-176000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5301000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-330000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4745000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-126000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-874000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-222000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-252000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-493000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-512000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-262000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-511000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-688000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15368000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-13050000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-66715000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1639000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>40638000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5298000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>27541000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5951000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>39747000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>31872000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>39828000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-69975000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>31551000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>11570000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>10172000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>20490000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-38719000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>15022000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>6689000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7614000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2245000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1270000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>571000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1056000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>923000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>225000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>37004000</v>
+      </c>
+      <c r="E21" s="3">
         <v>17130000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>29303000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>42699000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19332000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9670000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28748000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>36928000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>42565000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20190000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>51343000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12489000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>49780000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>49021000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>24867000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1530000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-52598000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9660000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>51658000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>15152000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>38393000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17201000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>48307000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>40513000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>37933000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-60464000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>39458000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>23023000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>20215000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>30064000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-30111000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>25542000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>17485000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>864000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>8744000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>7926000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>8425000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>7931000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>11610000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>12771000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1335000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1301000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1298000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1261000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1253000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1257000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1440000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1214000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1230000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1316000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1276000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1260000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1249000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1218000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2391,252 +2430,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32063000</v>
+      </c>
+      <c r="E23" s="3">
         <v>12319000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24456000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38105000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14750000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5148000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24025000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32508000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>38137000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15706000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46938000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16959000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45435000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>44752000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22109000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4258000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-55308000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6957000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>48953000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12484000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>35721000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>14528000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>45403000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>37930000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>35409000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-63049000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>36801000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20489000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17759000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>27647000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-32721000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>23147000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>15098000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1523000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>6391000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>5630000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>6129000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>5688000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>9314000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>10525000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6291000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2140000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5189000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7241000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2293000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>476000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4274000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6028000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7639000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2874000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9180000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4392000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9236000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8995000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3872000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1560000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-12066000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1252000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9055000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1840000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7296000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2688000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9273000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7517000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9002000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-13352000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7571000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3832000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3586000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5915000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-7028000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4440000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3021000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-452000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-27635400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1427000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1774000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1549000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>2959000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>3192000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2757,252 +2805,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25772000</v>
+      </c>
+      <c r="E26" s="3">
         <v>10179000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19267000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30864000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12457000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4672000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19751000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26480000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30498000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12832000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>37758000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12567000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>36199000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>35757000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18237000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2698000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-43242000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5705000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>39898000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10644000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>28425000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>11840000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>36130000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>30413000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>26407000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-49697000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>29230000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>16657000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>14173000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21732000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-25693000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>18707000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>12077000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1071000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>34026400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>4203000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>4355000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>4139000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>6355000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>7333000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>25667000</v>
+      </c>
+      <c r="E27" s="3">
         <v>10106000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19199000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30796000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12370000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4603000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19694000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26251000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30348000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12702000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>37574000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12767000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>35912000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35504000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18080000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2798000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-43621000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5580000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>39646000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10344000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>28094000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>11711000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>35835000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>30137000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26295000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-49746000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>29159000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>16524000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>14073000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>21661000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-25694000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>18540000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>12011000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1138000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>33921400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4067000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>4262000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>4060000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>6286000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>7198000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3123,8 +3180,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3197,8 +3257,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3215,11 +3275,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>302000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3227,11 +3287,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1370400</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3245,8 +3305,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3367,8 +3430,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3489,252 +3555,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E32" s="3">
         <v>176000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5301000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>330000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4745000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>126000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>874000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>222000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>252000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>493000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>512000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>262000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>511000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>688000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-15368000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>13050000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>66715000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1639000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-40638000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5298000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-27541000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5951000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-39747000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-31872000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-39828000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>69975000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-31551000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-11570000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-10172000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-20490000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>38719000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-15022000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-6689000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7614000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2245000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-571000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1056000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-923000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-225000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>25667000</v>
+      </c>
+      <c r="E33" s="3">
         <v>10106000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19199000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30796000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12370000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4603000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19694000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26251000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30348000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12702000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>37574000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12767000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>35912000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35504000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18080000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2798000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-43621000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5580000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>39646000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10344000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>28094000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>11711000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35835000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>30137000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>26295000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-49746000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>29159000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>16524000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>14073000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>21661000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-25392000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>18540000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>12011000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1138000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>32551000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4067000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>4262000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>4060000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>6286000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>7198000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3855,257 +3930,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>25667000</v>
+      </c>
+      <c r="E35" s="3">
         <v>10106000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19199000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30796000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12370000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4603000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19694000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26251000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30348000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12702000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>37574000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12767000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>35912000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35504000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18080000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2798000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-43621000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5580000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>39646000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10344000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>28094000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>11711000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35835000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>30137000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>26295000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-49746000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>29159000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>16524000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>14073000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>21661000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-25392000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>18540000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>12011000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1138000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>32551000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4067000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>4262000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>4060000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>6286000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>7198000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4148,8 +4232,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4192,175 +4277,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40609000</v>
+      </c>
+      <c r="E41" s="3">
         <v>58122000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>51877000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>76306000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100486000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42180000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>47729000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37181000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42324000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35549000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38022000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30840000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50055000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26747000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35811000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>32626000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30608000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39113000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>88184000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>69989000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>42298000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>60054000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>47990000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>26817000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>36074000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>42640000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>64175000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>74776000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>44634000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>26139000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>30361000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>41438000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>64561000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>57881000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>34796000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>42706000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>26418000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>87015000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>28048000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>84835000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>324905000</v>
+      </c>
+      <c r="E42" s="3">
         <v>339261000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>321434000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>305367000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>243605000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>305501000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>286472000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>288031000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>234618000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>153444000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>129619000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>126401000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>97322000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>103869000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4436,252 +4525,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>53197000</v>
+      </c>
+      <c r="E43" s="3">
         <v>51759000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48718000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>53460000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>51796000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51692000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48390000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>52046000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>52469000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>52835000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>51260000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>52726000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>51657000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>52488000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>48285000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>45368000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>44493000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>43055000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>39565000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>41601000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>40273000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>39052000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>35852000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>37815000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>36766000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>37957000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>35835000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>38267000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>37582000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>37170000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>35230000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>31884000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>31280000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>30906000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>32923000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>29652000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>28953000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>28870000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>27097000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>27544000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>29975000</v>
+      </c>
+      <c r="E44" s="3">
         <v>28723000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>27624000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>28519000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>27471000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>27034000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>27008000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>27617000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>27798000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>27770000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>25856000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24755000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>25295000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>25499000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>25366000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>25102000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>24560000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>22572000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>20954000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>20191000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>19393000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>18886000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>19208000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>19361000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>19277000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>20172000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>19852000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>19951000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>19834000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>19454000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>19069000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>16793000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>16194000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>16244000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>17366000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>16931000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>16442000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>16115000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>15727000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>15763000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4691,42 +4789,42 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>184000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>197000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>186000</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>292000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>241000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>238000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>334000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>470000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>355000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>504000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4802,53 +4900,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>449437000</v>
+      </c>
+      <c r="E46" s="3">
         <v>478553000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>450345000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>464483000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>424297000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>427268000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>410246000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>405978000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>358197000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>270447000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>245712000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>235956000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>225282000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>209658000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4924,374 +5025,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>360761000</v>
+      </c>
+      <c r="E47" s="3">
         <v>325654000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>335572000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>326708000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>308330000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>309914000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>318086000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>317825000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>331738000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>382616000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>406666000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>368552000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>403255000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>377130000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>477953000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>451909000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>462972000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>518262000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>463814000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>445128000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>466604000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>423491000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>428384000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>419394000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>372489000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>328471000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>365566000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>327271000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>332238000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>332955000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>307766000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>320362000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>277254000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>275691000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>323406000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>279069000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>284232000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>214610000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>266976000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>173599000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>244136000</v>
+      </c>
+      <c r="E48" s="3">
         <v>241744000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>241180000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>230565000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>227863000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>224758000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>228772000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>222272000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>219469000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>217500000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>221870000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>211498000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>209188000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>205855000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>196965000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>192989000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>192413000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>191760000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>191282000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>188875000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>188311000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>187356000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>187017000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>176253000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>174789000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>173421000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>180282000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>177486000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>175560000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>173624000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>166706000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>165017000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>163229000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>162112000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>219470000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>156829000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>154909000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>153645000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>152773000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>152068000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>118108000</v>
+      </c>
+      <c r="E49" s="3">
         <v>118467000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>117916000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>119643000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>119421000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>119448000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>119654000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>120852000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>120767000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>121298000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>121766000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>122856000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>123519000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>122148000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>108598000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>102163000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>102722000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>103165000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>103512000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>103575000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>103791000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>104080000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>104418000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>102077000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>102172000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>112936000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>113528000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>112629000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>112927000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>113124000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>113173000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>113617000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>113844000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>114256000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>115933000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>114507000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>113986000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>114026000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>113572000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>115044000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5412,8 +5525,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5534,130 +5650,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>52230000</v>
+      </c>
+      <c r="E52" s="3">
         <v>49900000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34423000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>46939000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>46861000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>46385000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35928000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>44333000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43540000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43421000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35188000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>47797000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>47345000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>49438000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10458000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10720000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10829000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10973000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11161000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12138000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12374000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12595000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12847000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>13469000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>13650000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>13945000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>13747000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>13359000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>13634000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>13831000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>14104000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>14451000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>14730000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>15007000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>15278000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>13572000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>13597000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>13830000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>8047000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>7505000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5778,130 +5900,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1263071000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1252271000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1222176000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1225963000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1163968000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1164532000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1153881000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1147251000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1108860000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1070035000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1069978000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1019933000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1041573000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>997072000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>948465000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>902296000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>909860000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>969506000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>958784000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>920758000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>912493000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>884393000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>873729000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>829946000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>788133000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>760448000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>817729000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>788482000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>760108000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>738724000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>707794000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>736459000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>711932000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>702651000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>702095000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>681554000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>665590000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>654451000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>620854000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>604038000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5944,8 +6072,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5988,419 +6117,429 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>61846000</v>
+      </c>
+      <c r="E57" s="3">
         <v>58215000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50979000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56817000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55152000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54762000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>49719000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56247000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53316000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>51937000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>49351000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>54879000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>51924000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>52238000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>49816000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>47971000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>47580000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>46005000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>46072000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>47132000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>45544000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>43693000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>44503000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>44026000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40665000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>39428000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>36361000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>35241000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>34568000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>33708000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>37075000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>40119000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>38939000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>38029000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>37291000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>34960000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>33668000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>32967000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>34897000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>35434000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2663000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2243000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11219000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3039000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2986000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1921000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3929000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2024000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2254000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2658000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6757000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2524000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3066000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3517000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2429000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1815000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2241000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2155000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2351000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2265000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2922000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3488000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3348000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3360000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3158000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3555000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4686000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4499000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4261000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3910000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4373000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3517000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5219000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>4408000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1832000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1819000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2013000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2135000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>2094000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>2019000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>90947000</v>
+      </c>
+      <c r="E59" s="3">
         <v>105914000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1525000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>110771000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>83209000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100626000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15076000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>107221000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>101695000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95946000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>878000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>85991000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>93320000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>86493000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28657000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26878000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25727000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>25368000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>23512000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>25239000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23732000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>27840000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21395000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>28813000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22106000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>30348000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>25664000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>34739000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>26013000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>26172000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18093000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>19011000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18292000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18448000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>16040000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>16552000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>16129000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>16106000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>14245000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>15223000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>155456000</v>
+      </c>
+      <c r="E60" s="3">
         <v>166372000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>63723000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>170627000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>141347000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>157309000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>68724000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>165492000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>157265000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>150541000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56986000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>143394000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>148310000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>142248000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6476,252 +6615,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>125936000</v>
+      </c>
+      <c r="E61" s="3">
         <v>126643000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>124152000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>124204000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>124034000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>124006000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>126829000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>122483000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>121374000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>120096000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>126813000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>122257000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>122281000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>120107000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>120315000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>114681000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>116840000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>117506000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>111911000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>112700000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>112301000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>111043000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>113547000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>104331000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>103531000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>100678000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>98682000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>97695000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>95646000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>93283000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>93117000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>94123000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>91554000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>94677000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>100755000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>99671000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>100257000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>101821000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>99550000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>99779000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>198748000</v>
+      </c>
+      <c r="E62" s="3">
         <v>197053000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>197662000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>197208000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>195897000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>194169000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>192302000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>194473000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>190065000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>189638000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>192558000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>187641000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>188048000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>188098000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>77368000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>74155000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>77268000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>91114000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>90243000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>82248000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>81577000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>76392000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>74098000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>67340000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>61270000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>52571000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>66799000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>60389000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>59622000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>56852000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>51375000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>59340000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>56514000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>55718000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>56607000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>86559000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>84314000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>82132000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>77442000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>73570000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6842,8 +6990,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6964,8 +7115,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7086,130 +7240,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>512894000</v>
+      </c>
+      <c r="E66" s="3">
         <v>522821000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>502473000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>525522000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>493692000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>507790000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>502226000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>515445000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>500889000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>492250000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>499208000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>485206000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>489812000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>480812000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>475041000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>446866000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>448631000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>461365000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>452585000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>448278000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>442084000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>436406000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>430565000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>414791000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>394638000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>388883000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>392938000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>390873000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>377564000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>369847000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>359091000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>360853000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>353838000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>355250000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>353799000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>373276000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>364931000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>361600000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>338784000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>334774000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7252,8 +7412,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7374,8 +7535,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7496,8 +7660,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7618,8 +7785,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7740,130 +7910,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>798959000</v>
+      </c>
+      <c r="E72" s="3">
         <v>773292000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>763186000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>743987000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>713191000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>700821000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>696218000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>676524000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>650273000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>619925000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>607350000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>569776000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>582543000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>546631000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>511127000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>493438000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>496126000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>539881000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>534421000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>494775000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>484431000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>456337000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>444626000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>408791000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>378654000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>352359000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>402493000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>373334000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>356846000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>342773000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>321112000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>346503000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>327963000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>315952000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>255786000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>224166000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>220099000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>215837000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>210846000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>205491000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7984,8 +8160,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8106,8 +8285,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8228,130 +8410,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>747910000</v>
+      </c>
+      <c r="E76" s="3">
         <v>727181000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>717419000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>698155000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>667989000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>654471000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>649368000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>629069000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>601697000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>571490000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>561273000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>525330000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>539883000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>504554000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>473424000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>455430000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>461229000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>508141000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>506199000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>472480000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>470409000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>447987000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>443164000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>415155000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>393495000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>371565000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>424791000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>397609000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>382544000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>368877000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>348703000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>375606000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>358094000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>347401000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>348296000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>308278000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>300659000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>292851000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>282070000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>269264000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8472,257 +8660,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>25667000</v>
+      </c>
+      <c r="E81" s="3">
         <v>10106000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19199000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30796000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12370000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4603000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19694000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26251000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30348000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12702000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>37574000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12767000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>35912000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35504000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18080000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2798000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-43621000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5580000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>39646000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10344000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>28094000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>11711000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35835000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>30137000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>26295000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-49746000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>29159000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>16524000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>14073000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>21661000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-25392000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>18540000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>12011000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1138000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>32551000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4067000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>4262000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>4060000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>6286000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>7198000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8765,130 +8962,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2910000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2821000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2783000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2798000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2741000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2733000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2629000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2782000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2653000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2622000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2430000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2425000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2411000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2400000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2758000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2728000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2710000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2703000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2705000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2668000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2672000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2673000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2904000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2583000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2524000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2585000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2657000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2534000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2456000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2417000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2610000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2395000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>2387000</v>
       </c>
       <c r="AJ83" s="3">
         <v>2387000</v>
       </c>
       <c r="AK83" s="3">
+        <v>2387000</v>
+      </c>
+      <c r="AL83" s="3">
         <v>2353000</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>2296000</v>
       </c>
       <c r="AM83" s="3">
         <v>2296000</v>
       </c>
       <c r="AN83" s="3">
+        <v>2296000</v>
+      </c>
+      <c r="AO83" s="3">
         <v>2243000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2296000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>2246000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9009,8 +9210,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9131,8 +9335,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9253,8 +9460,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9375,8 +9585,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9497,130 +9710,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11215000</v>
+      </c>
+      <c r="E89" s="3">
         <v>10438000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11192000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13789000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10085000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10903000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4621000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1803000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13602000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10566000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14400000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13669000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12434000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8693000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10311000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11678000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8532000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6829000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7795000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>12067000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10253000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9306000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10546000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11761000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>10668000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6798000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>12077000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>9848000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>9185000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7577000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10845000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>10464000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>8535000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7556000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>8277000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>10872000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>8322000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>18305000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>7364000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>9860000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9663,130 +9882,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5645000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4986000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6202000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5586000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4858000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4281000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5347000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4701000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4535000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4393000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5708000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5303000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4685000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3713000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4557000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4074000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3743000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3090000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4032000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3581000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3144000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2519000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3496000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3329000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3219000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2968000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4840000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4392000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3596000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3151000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4497000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3711000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3740000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2589000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3297000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3262000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2794000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-4710000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>5904000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-6570000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9907,8 +10130,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10029,130 +10255,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24336000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4308000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-38392000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-39052000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>49358000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16401000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4268000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3904000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7448000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3203000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7351000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28048000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>10655000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7919000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6092000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7336000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15607000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-58566000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>17311000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>23514000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-22629000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>11196000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>16649000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11855000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-14747000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-27804000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-21077000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>18364000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>7293000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-10201000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-21818000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-33461000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>122000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>22308000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-19863000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>6825000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-5505000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-22466000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-60015000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>1865000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10195,8 +10427,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10239,8 +10472,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10317,8 +10550,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10439,8 +10675,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10561,8 +10800,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10683,370 +10925,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4283000</v>
+      </c>
+      <c r="E100" s="3">
         <v>174000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2511000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>835000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1166000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>53000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1653000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3065000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>854000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9802000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-136000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4636000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>289000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9922000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1351000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1918000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1036000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2643000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7144000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7786000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5229000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8349000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6668000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8856000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2474000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-346000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1779000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2098000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2089000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1678000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-286000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1722000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3794000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>469000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1398000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2484000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2015000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>595000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>443000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-76000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-158000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>87000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-97000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-44000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>126000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-34000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>47000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>175000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-296000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-326000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>53000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>285000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-276000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-327000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>50000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>103000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>14000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-51000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>432000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>44000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-184000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>120000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-121000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>11000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>15000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-31000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-68000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-133000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>92000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>26000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>39000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>122000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>61000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-162000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17450000</v>
+      </c>
+      <c r="E102" s="3">
         <v>6241000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-24542000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24117000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>58373000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5521000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10384000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5079000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6911000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2483000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7039000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19049000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23355000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9101000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3043000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2132000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8438000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-49044000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18065000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>27809000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-17656000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12092000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>20959000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-9150000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6509000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-21536000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10659000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>30189000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>18578000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4287000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-11290000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-23075000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6802000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>26162000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-11139000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>16338000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>455000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-2085000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-52218000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>12156000</v>
       </c>
     </row>
